--- a/Result/profitability/8463.xlsx
+++ b/Result/profitability/8463.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM52"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7034,6 +7034,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>8463</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1707</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E53" t="n">
+        <v>262</v>
+      </c>
+      <c r="F53" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="G53" t="n">
+        <v>151</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>159</v>
+      </c>
+      <c r="K53" t="n">
+        <v>93</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="N53" t="n">
+        <v>12.85875</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.4761904761904763</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.2275641025641026</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-0.1948051948051949</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.08115737473535645</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
